--- a/data/processed/positivacao/2026-04_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2026-04_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -27389,7 +27389,7 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1041" t="inlineStr"/>
@@ -36193,7 +36193,7 @@
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr"/>
@@ -66931,7 +66931,7 @@
     <row r="2563">
       <c r="A2563" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2563" t="inlineStr"/>
@@ -68576,12 +68576,12 @@
       <c r="A2627" t="inlineStr"/>
       <c r="B2627" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 7 cliente(s), não positivou 80 cliente(s) - Total vendido: R$ 7.279,27
+          <t>Vendedor 1 - VENDEDOR 01: positivou 7 cliente(s), não positivou 80 cliente(s) - Total vendido: R$ 7.279,27
 Vendedor 18 - LOJA: positivou 331 cliente(s), não positivou 613 cliente(s) - Total vendido: R$ 125.318,48
-Vendedor 3 - FERNANDA: positivou 22 cliente(s), não positivou 316 cliente(s) - Total vendido: R$ 7.125,78
-Vendedor 4 - DANIELA: positivou 252 cliente(s), não positivou 485 cliente(s) - Total vendido: R$ 211.980,10
+Vendedor 3 - VENDEDOR 03: positivou 22 cliente(s), não positivou 316 cliente(s) - Total vendido: R$ 7.125,78
+Vendedor 4 - VENDEDOR 04: positivou 252 cliente(s), não positivou 485 cliente(s) - Total vendido: R$ 211.980,10
 Vendedor 5 - SITE: positivou 3 cliente(s), não positivou 441 cliente(s) - Total vendido: R$ 583,61
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2627" t="inlineStr"/>
